--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486540_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486540_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0779</v>
+        <v>4.421</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9996</v>
+        <v>3.5584</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0783</v>
+        <v>0.8626</v>
       </c>
       <c r="G2" t="n">
         <v>1.8469</v>
@@ -610,13 +610,13 @@
         <v>1.305</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0136</v>
+        <v>0.3566</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6165</v>
+        <v>-0.0577</v>
       </c>
       <c r="U2" t="n">
-        <v>0.63</v>
+        <v>0.4143</v>
       </c>
       <c r="V2" t="n">
         <v>1.13</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9585</v>
+        <v>3.264</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2337</v>
+        <v>2.6317</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7248</v>
+        <v>0.6323</v>
       </c>
       <c r="G3" t="n">
         <v>0.2408</v>
@@ -688,13 +688,13 @@
         <v>2.1751</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1304</v>
+        <v>0.4359</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4817</v>
+        <v>0.8797</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3513</v>
+        <v>-0.4437</v>
       </c>
       <c r="V3" t="n">
         <v>1.4997</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. KRAVIC</t>
+          <t>R. ANDERSSON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2832</v>
+        <v>3.0437</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2022</v>
+        <v>1.4443</v>
       </c>
       <c r="F4" t="n">
-        <v>0.081</v>
+        <v>1.5995</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8768</v>
+        <v>2.6404</v>
       </c>
       <c r="H4" t="n">
-        <v>3.0537</v>
+        <v>0.5686</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1769</v>
+        <v>2.0718</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9996</v>
+        <v>1.7002</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9231</v>
+        <v>0.438</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0765</v>
+        <v>1.2622</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1228</v>
+        <v>0.9402</v>
       </c>
       <c r="N4" t="n">
         <v>0.1306</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2534</v>
+        <v>0.8096</v>
       </c>
       <c r="P4" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8409</v>
+        <v>-0.316</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9421</v>
+        <v>-0.256</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1012</v>
+        <v>-0.0601</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.3045</v>
+        <v>-0.5857</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.5857</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. ANDERSSON</t>
+          <t>D. KRAVIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8202</v>
+        <v>2.551</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2207</v>
+        <v>2.5316</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5995</v>
+        <v>0.0194</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6404</v>
+        <v>2.8768</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5686</v>
+        <v>3.0537</v>
       </c>
       <c r="I5" t="n">
-        <v>2.0718</v>
+        <v>-0.1769</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7002</v>
+        <v>2.9996</v>
       </c>
       <c r="K5" t="n">
-        <v>0.438</v>
+        <v>2.9231</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2622</v>
+        <v>0.0765</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9402</v>
+        <v>-0.1228</v>
       </c>
       <c r="N5" t="n">
         <v>0.1306</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8096</v>
+        <v>-0.2534</v>
       </c>
       <c r="P5" t="n">
-        <v>1.305</v>
+        <v>0.87</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.305</v>
+        <v>0.87</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5396</v>
+        <v>0.1088</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4795</v>
+        <v>0.2716</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0601</v>
+        <v>-0.1628</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5857</v>
+        <v>-1.3045</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5857</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9364</v>
+        <v>2.5136</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0036</v>
+        <v>2.5191</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0672</v>
+        <v>-0.0055</v>
       </c>
       <c r="G6" t="n">
         <v>1.7445</v>
@@ -922,13 +922,13 @@
         <v>2.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0034</v>
+        <v>0.5738</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.5071</v>
       </c>
       <c r="U6" t="n">
-        <v>0.005</v>
+        <v>0.0667</v>
       </c>
       <c r="V6" t="n">
         <v>0.1952</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. DOS ANJOS DE PAULA</t>
+          <t>S. QUINTELA SALVADOR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8499</v>
+        <v>0.4019</v>
       </c>
       <c r="E7" t="n">
-        <v>2.107</v>
+        <v>1.0479</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.257</v>
+        <v>-0.646</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.2601</v>
+        <v>-1.3906</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.558</v>
+        <v>0.0246</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7020999999999999</v>
+        <v>-1.4152</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.4613</v>
+        <v>-0.2359</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.8821</v>
+        <v>0.3745</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4207</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.7987</v>
+        <v>-1.1548</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.6759</v>
+        <v>-0.3499</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.1228</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>0.435</v>
+        <v>1.305</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.6101</v>
+        <v>1.305</v>
       </c>
       <c r="S7" t="n">
-        <v>2.4151</v>
+        <v>-0.0775</v>
       </c>
       <c r="T7" t="n">
-        <v>2.1583</v>
+        <v>0.1538</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2568</v>
+        <v>-0.2313</v>
       </c>
       <c r="V7" t="n">
-        <v>2.2599</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>3.5851</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.3252</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. QUINTELA SALVADOR</t>
+          <t>F. DOS ANJOS DE PAULA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2054</v>
+        <v>0.0166</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1597</v>
+        <v>1.0579</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9543</v>
+        <v>-1.0413</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3906</v>
+        <v>-4.2601</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0246</v>
+        <v>-3.558</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.4152</v>
+        <v>-0.7020999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2359</v>
+        <v>-1.4613</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3745</v>
+        <v>-1.8821</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6104000000000001</v>
+        <v>0.4207</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1548</v>
+        <v>-2.7987</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3499</v>
+        <v>-1.6759</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-1.1228</v>
       </c>
       <c r="P8" t="n">
-        <v>1.305</v>
+        <v>0.435</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R8" t="n">
-        <v>1.305</v>
+        <v>2.6101</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.274</v>
+        <v>1.5817</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2656</v>
+        <v>1.1092</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5396</v>
+        <v>0.4726</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5649999999999999</v>
+        <v>2.2599</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>3.5851</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ETXEGUREN GONZALEZ</t>
+          <t>A. GALAN POZO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4</v>
+        <v>-0.1639</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2175</v>
+        <v>2.2128</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1825</v>
+        <v>-2.3766</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1825</v>
+        <v>-1.5987</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1825</v>
+        <v>0.368</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-1.9667</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1.6311</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1.4964</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.1347</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1825</v>
+        <v>-3.2298</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1825</v>
+        <v>-1.1284</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-2.1013</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2175</v>
+        <v>1.5225</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.2175</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.7401</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.2374</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.7991</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.4383</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. GALAN POZO</t>
+          <t>A. ETXEGUREN GONZALEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6871</v>
+        <v>-0.4</v>
       </c>
       <c r="E10" t="n">
-        <v>1.4737</v>
+        <v>-0.2175</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1609</v>
+        <v>-0.1825</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5987</v>
+        <v>-0.1825</v>
       </c>
       <c r="H10" t="n">
-        <v>0.368</v>
+        <v>-0.1825</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.9667</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6311</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4964</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1347</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.2298</v>
+        <v>-0.1825</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1284</v>
+        <v>-0.1825</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.1013</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5225</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.2175</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7401</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7141999999999999</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0601</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6541</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. MUNNINGS</t>
+          <t>L. WESTERMANN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8532999999999999</v>
+        <v>-1.3389</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2634</v>
+        <v>-1.1696</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.59</v>
+        <v>-0.1694</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.6162</v>
+        <v>0.3882</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5141</v>
+        <v>-1.2438</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.1021</v>
+        <v>1.632</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.714</v>
+        <v>1.9725</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2007</v>
+        <v>-0.2309</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.9147999999999999</v>
+        <v>2.2034</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9022</v>
+        <v>-1.5843</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7149</v>
+        <v>-1.0129</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.1873</v>
+        <v>-0.5714</v>
       </c>
       <c r="P11" t="n">
-        <v>1.5225</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.2175</v>
+        <v>-4.5676</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7401</v>
+        <v>2.1751</v>
       </c>
       <c r="S11" t="n">
-        <v>1.9353</v>
+        <v>0.6654</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6682</v>
+        <v>0.2956</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2672</v>
+        <v>0.3698</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.695</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.695</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L. WESTERMANN</t>
+          <t>T. MUNNINGS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6791</v>
+        <v>-1.4545</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3557</v>
+        <v>-0.7104</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3235</v>
+        <v>-0.7441</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3882</v>
+        <v>-2.6162</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.2438</v>
+        <v>-0.5141</v>
       </c>
       <c r="I12" t="n">
-        <v>1.632</v>
+        <v>-2.1021</v>
       </c>
       <c r="J12" t="n">
-        <v>1.9725</v>
+        <v>-0.714</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2309</v>
+        <v>0.2007</v>
       </c>
       <c r="L12" t="n">
-        <v>2.2034</v>
+        <v>-0.9147999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.5843</v>
+        <v>-1.9022</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.0129</v>
+        <v>-0.7149</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5714</v>
+        <v>-1.1873</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.3926</v>
+        <v>1.5225</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.5676</v>
+        <v>-0.2175</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1751</v>
+        <v>1.7401</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6748</v>
+        <v>1.3342</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8904</v>
+        <v>0.2211</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2157</v>
+        <v>1.1131</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.13</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="13">
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>12.512</v>
+        <v>12.8545</v>
       </c>
       <c r="E13" t="n">
-        <v>14.5636</v>
+        <v>14.9062</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.0518</v>
+        <v>-2.0516</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3105000000000014</v>
+        <v>-0.3105000000000016</v>
       </c>
       <c r="H13" t="n">
         <v>-1.9002</v>
@@ -1456,10 +1456,10 @@
         <v>-7.726500000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-6.880999999999999</v>
+        <v>-6.880999999999998</v>
       </c>
       <c r="P13" t="n">
-        <v>6.524900000000001</v>
+        <v>6.5249</v>
       </c>
       <c r="Q13" t="n">
         <v>-10.8753</v>
@@ -1468,16 +1468,16 @@
         <v>17.4006</v>
       </c>
       <c r="S13" t="n">
-        <v>5.5577</v>
+        <v>5.900300000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>3.5812</v>
+        <v>3.9235</v>
       </c>
       <c r="U13" t="n">
-        <v>1.9766</v>
+        <v>1.9769</v>
       </c>
       <c r="V13" t="n">
-        <v>0.7393999999999992</v>
+        <v>0.7393999999999996</v>
       </c>
       <c r="W13" t="n">
         <v>7.5608</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.1485</v>
+        <v>3.1176</v>
       </c>
       <c r="E14" t="n">
         <v>4.6088</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4603</v>
+        <v>-1.4912</v>
       </c>
       <c r="G14" t="n">
         <v>2.8438</v>
@@ -1546,13 +1546,13 @@
         <v>1.0875</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4556</v>
+        <v>-0.4864</v>
       </c>
       <c r="T14" t="n">
         <v>0.0721</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5276999999999999</v>
+        <v>-0.5585</v>
       </c>
       <c r="V14" t="n">
         <v>0.7602</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2003</v>
+        <v>2.4854</v>
       </c>
       <c r="E15" t="n">
-        <v>4.7084</v>
+        <v>4.9319</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.5081</v>
+        <v>-2.4464</v>
       </c>
       <c r="G15" t="n">
         <v>1.2828</v>
@@ -1624,13 +1624,13 @@
         <v>1.5225</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.735</v>
+        <v>-1.4499</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.5179</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9936</v>
+        <v>-0.9319</v>
       </c>
       <c r="V15" t="n">
         <v>1.13</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8346</v>
+        <v>1.5417</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0966</v>
+        <v>2.6496</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.262</v>
+        <v>-1.1079</v>
       </c>
       <c r="G16" t="n">
         <v>2.0864</v>
@@ -1702,13 +1702,13 @@
         <v>1.0875</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2518</v>
+        <v>-0.5447</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1286</v>
+        <v>-0.3184</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3803</v>
+        <v>-0.2262</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. GIOVANNETTI</t>
+          <t>A. GONZÁLEZ PÉREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6996</v>
+        <v>0.149</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2717</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9713000000000001</v>
+        <v>0.149</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8401999999999999</v>
+        <v>0.149</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8242</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0159</v>
+        <v>0.149</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.2824</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6903</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5921</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4422</v>
+        <v>0.149</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1339</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.149</v>
       </c>
       <c r="P17" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6697</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0106</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3409</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. GONZÁLEZ PÉREZ</t>
+          <t>L. GIOVANNETTI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.149</v>
+        <v>0.1215</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>-0.9423</v>
       </c>
       <c r="F18" t="n">
-        <v>0.149</v>
+        <v>1.0638</v>
       </c>
       <c r="G18" t="n">
-        <v>0.149</v>
+        <v>-0.8401999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-0.8242</v>
       </c>
       <c r="I18" t="n">
-        <v>0.149</v>
+        <v>-0.0159</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-1.2824</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-0.6903</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.5921</v>
       </c>
       <c r="M18" t="n">
-        <v>0.149</v>
+        <v>0.4422</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.1339</v>
       </c>
       <c r="O18" t="n">
-        <v>0.149</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.0916</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.3401</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>-0.2485</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0222</v>
+        <v>0.1031</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1917</v>
+        <v>2.3035</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1696</v>
+        <v>-2.2004</v>
       </c>
       <c r="G19" t="n">
         <v>0.7943</v>
@@ -1936,13 +1936,13 @@
         <v>1.0875</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1201</v>
+        <v>-1.0392</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.6297</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3787</v>
+        <v>-0.4095</v>
       </c>
       <c r="V19" t="n">
         <v>-0.7395</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. SALIN</t>
+          <t>H. LOPEZ BARRANTES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1177</v>
+        <v>-1.7573</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3706</v>
+        <v>-0.1423</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2529</v>
+        <v>-1.615</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.5947</v>
+        <v>0.1378</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0484</v>
+        <v>-0.0335</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.6431</v>
+        <v>0.1713</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.0001</v>
+        <v>0.1912</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2007</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2008</v>
+        <v>0.1912</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5946</v>
+        <v>-0.0534</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1523</v>
+        <v>-0.0335</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4423</v>
+        <v>-0.0199</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6525</v>
+        <v>-0.435</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5655</v>
+        <v>-0.1349</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8904</v>
+        <v>0.5588</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.675</v>
+        <v>-0.6937</v>
       </c>
       <c r="V21" t="n">
-        <v>1.695</v>
+        <v>-1.3252</v>
       </c>
       <c r="W21" t="n">
-        <v>1.695</v>
+        <v>0.1952</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.5204</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>H. LOPEZ BARRANTES</t>
+          <t>S. SALIN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3469</v>
+        <v>-1.8017</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7010999999999999</v>
+        <v>-2.1471</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6458</v>
+        <v>0.3454</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1378</v>
+        <v>-1.5947</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0335</v>
+        <v>0.0484</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1713</v>
+        <v>-1.6431</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1912</v>
+        <v>-1.0001</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>0.2007</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1912</v>
+        <v>-1.2008</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.0534</v>
+        <v>-0.5946</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0335</v>
+        <v>-0.1523</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0199</v>
+        <v>-0.4423</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.435</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7245</v>
+        <v>-1.2495</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>-0.6669</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7245</v>
+        <v>-0.5825</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.3252</v>
+        <v>1.695</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1952</v>
+        <v>1.695</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.5204</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5182</v>
+        <v>-2.549</v>
       </c>
       <c r="E23" t="n">
         <v>-0.8564000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6619</v>
+        <v>-1.6927</v>
       </c>
       <c r="G23" t="n">
         <v>0.4649</v>
@@ -2248,13 +2248,13 @@
         <v>0.435</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1131</v>
+        <v>-0.1439</v>
       </c>
       <c r="T23" t="n">
         <v>-0.548</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4349</v>
+        <v>0.4041</v>
       </c>
       <c r="V23" t="n">
         <v>-1.13</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.8927</v>
+        <v>-6.1585</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.5101</v>
+        <v>-3.6219</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.3825</v>
+        <v>-2.5367</v>
       </c>
       <c r="G24" t="n">
         <v>-2.0048</v>
@@ -2326,13 +2326,13 @@
         <v>0.6525</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3323</v>
+        <v>0.0664</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0036</v>
+        <v>-0.1081</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3287</v>
+        <v>0.1745</v>
       </c>
       <c r="V24" t="n">
         <v>0.5649999999999999</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.3479</v>
+        <v>-6.421</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.0487</v>
+        <v>-3.9369</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.2992</v>
+        <v>-2.4841</v>
       </c>
       <c r="G25" t="n">
         <v>-1.7345</v>
@@ -2404,13 +2404,13 @@
         <v>1.9576</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5259</v>
+        <v>-0.599</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2019</v>
+        <v>-0.0901</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.324</v>
+        <v>-0.5089</v>
       </c>
       <c r="V25" t="n">
         <v>-1.695</v>
@@ -2440,19 +2440,19 @@
         <v>-12.512</v>
       </c>
       <c r="E26" t="n">
-        <v>2.051599999999999</v>
+        <v>2.051599999999998</v>
       </c>
       <c r="F26" t="n">
         <v>-14.5637</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3104999999999996</v>
+        <v>0.3105000000000004</v>
       </c>
       <c r="H26" t="n">
         <v>1.9002</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.589599999999999</v>
+        <v>-1.5896</v>
       </c>
       <c r="J26" t="n">
         <v>14.6075</v>
@@ -2467,7 +2467,7 @@
         <v>-14.297</v>
       </c>
       <c r="N26" t="n">
-        <v>-5.826299999999999</v>
+        <v>-5.8263</v>
       </c>
       <c r="O26" t="n">
         <v>-8.470899999999999</v>
@@ -2482,22 +2482,22 @@
         <v>10.8751</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.558</v>
+        <v>-5.558000000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.9767</v>
+        <v>-1.9766</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.581100000000001</v>
+        <v>-3.5811</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.7395</v>
+        <v>-0.7395000000000003</v>
       </c>
       <c r="W26" t="n">
-        <v>6.821199999999999</v>
+        <v>6.821200000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>-7.560799999999999</v>
+        <v>-7.5608</v>
       </c>
     </row>
   </sheetData>
